--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126807174</v>
+        <v>126807124</v>
       </c>
       <c r="B3" t="n">
-        <v>78738</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443147</v>
+        <v>443128</v>
       </c>
       <c r="R3" t="n">
-        <v>6764845</v>
+        <v>6764859</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126807124</v>
+        <v>126807174</v>
       </c>
       <c r="B4" t="n">
-        <v>91265</v>
+        <v>78769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443128</v>
+        <v>443147</v>
       </c>
       <c r="R4" t="n">
-        <v>6764859</v>
+        <v>6764845</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>126806596</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126807138</v>
       </c>
       <c r="B6" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126809153</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>126809061</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126807192</v>
+        <v>126806915</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>91339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443147</v>
+        <v>443009</v>
       </c>
       <c r="R9" t="n">
-        <v>6764845</v>
+        <v>6764878</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126806915</v>
+        <v>126807192</v>
       </c>
       <c r="B10" t="n">
-        <v>91265</v>
+        <v>78770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443009</v>
+        <v>443147</v>
       </c>
       <c r="R10" t="n">
-        <v>6764878</v>
+        <v>6764845</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,7 +1768,7 @@
         <v>126807424</v>
       </c>
       <c r="B12" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126807279</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126807368</v>
       </c>
       <c r="B14" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,45 +2091,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126809036</v>
+        <v>126806928</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443235</v>
+        <v>443009</v>
       </c>
       <c r="R15" t="n">
-        <v>6764959</v>
+        <v>6764877</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2161,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2171,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,50 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126806928</v>
+        <v>126809036</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>78770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443009</v>
+        <v>443235</v>
       </c>
       <c r="R16" t="n">
-        <v>6764877</v>
+        <v>6764959</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126808925</v>
+        <v>126806993</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,39 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443278</v>
+        <v>443056</v>
       </c>
       <c r="R17" t="n">
-        <v>6764930</v>
+        <v>6764863</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2385,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2395,7 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tallar flera</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,45 +2422,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126807104</v>
+        <v>126808925</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443143</v>
+        <v>443278</v>
       </c>
       <c r="R18" t="n">
-        <v>6764853</v>
+        <v>6764930</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2492,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,12 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,45 +2534,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126806993</v>
+        <v>126807104</v>
       </c>
       <c r="B19" t="n">
-        <v>56849</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443056</v>
+        <v>443143</v>
       </c>
       <c r="R19" t="n">
-        <v>6764863</v>
+        <v>6764853</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tjäderbetat tallar flera</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2649,7 @@
         <v>126809217</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126856462</v>
+        <v>126856440</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442988</v>
+        <v>442971</v>
       </c>
       <c r="R21" t="n">
-        <v>6764821</v>
+        <v>6764763</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126856440</v>
+        <v>126856462</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442971</v>
+        <v>442988</v>
       </c>
       <c r="R22" t="n">
-        <v>6764763</v>
+        <v>6764821</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2960,43 +2960,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126856543</v>
+        <v>126856452</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3004,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443237</v>
+        <v>443002</v>
       </c>
       <c r="R23" t="n">
-        <v>6765007</v>
+        <v>6764790</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3067,37 +3061,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126856452</v>
+        <v>126856543</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443002</v>
+        <v>443237</v>
       </c>
       <c r="R24" t="n">
-        <v>6764790</v>
+        <v>6765007</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3171,7 +3171,7 @@
         <v>126856401</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>126856468</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126856408</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>126856520</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126856512</v>
+        <v>126856433</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443245</v>
+        <v>442967</v>
       </c>
       <c r="R31" t="n">
-        <v>6765041</v>
+        <v>6764772</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126856433</v>
+        <v>126856512</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442967</v>
+        <v>443245</v>
       </c>
       <c r="R32" t="n">
-        <v>6764772</v>
+        <v>6765041</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126807124</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126807174</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126806596</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126807138</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126809153</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>126809061</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126806915</v>
       </c>
       <c r="B9" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,45 +1546,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126807192</v>
+        <v>126806622</v>
       </c>
       <c r="B10" t="n">
-        <v>78770</v>
+        <v>56849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443147</v>
+        <v>442916</v>
       </c>
       <c r="R10" t="n">
-        <v>6764845</v>
+        <v>6764851</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,45 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126806622</v>
+        <v>126807192</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442916</v>
+        <v>443147</v>
       </c>
       <c r="R11" t="n">
-        <v>6764851</v>
+        <v>6764845</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,12 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,7 +1768,7 @@
         <v>126807424</v>
       </c>
       <c r="B12" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126807279</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126807368</v>
       </c>
       <c r="B14" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>126809036</v>
       </c>
       <c r="B16" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126806993</v>
+        <v>126808925</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,34 +2321,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443056</v>
+        <v>443278</v>
       </c>
       <c r="R17" t="n">
-        <v>6764863</v>
+        <v>6764930</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2385,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2395,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tallar flera</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,50 +2422,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126808925</v>
+        <v>126807104</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443278</v>
+        <v>443143</v>
       </c>
       <c r="R18" t="n">
-        <v>6764930</v>
+        <v>6764853</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2497,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2502,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,45 +2534,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126807104</v>
+        <v>126806993</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443143</v>
+        <v>443056</v>
       </c>
       <c r="R19" t="n">
-        <v>6764853</v>
+        <v>6764863</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Tjäderbetat tallar flera</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2649,7 @@
         <v>126809217</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>126856440</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>126856462</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>126856452</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>126856401</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>126856468</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126856408</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>126856520</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>126856433</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>126856512</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126807124</v>
+        <v>126807174</v>
       </c>
       <c r="B3" t="n">
-        <v>91345</v>
+        <v>78772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443128</v>
+        <v>443147</v>
       </c>
       <c r="R3" t="n">
-        <v>6764859</v>
+        <v>6764845</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126807174</v>
+        <v>126807124</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>91345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443147</v>
+        <v>443128</v>
       </c>
       <c r="R4" t="n">
-        <v>6764845</v>
+        <v>6764859</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126806915</v>
+        <v>126807192</v>
       </c>
       <c r="B9" t="n">
-        <v>91345</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443009</v>
+        <v>443147</v>
       </c>
       <c r="R9" t="n">
-        <v>6764878</v>
+        <v>6764845</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126806622</v>
+        <v>126806915</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>91345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442916</v>
+        <v>443009</v>
       </c>
       <c r="R10" t="n">
-        <v>6764851</v>
+        <v>6764878</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,45 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126807192</v>
+        <v>126806622</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443147</v>
+        <v>442916</v>
       </c>
       <c r="R11" t="n">
-        <v>6764845</v>
+        <v>6764851</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1728,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1733,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126808925</v>
+        <v>126806993</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,39 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443278</v>
+        <v>443056</v>
       </c>
       <c r="R17" t="n">
-        <v>6764930</v>
+        <v>6764863</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2385,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2395,7 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tallar flera</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,45 +2422,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126807104</v>
+        <v>126808925</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443143</v>
+        <v>443278</v>
       </c>
       <c r="R18" t="n">
-        <v>6764853</v>
+        <v>6764930</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2492,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,12 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,45 +2534,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126806993</v>
+        <v>126807104</v>
       </c>
       <c r="B19" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443056</v>
+        <v>443143</v>
       </c>
       <c r="R19" t="n">
-        <v>6764863</v>
+        <v>6764853</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tjäderbetat tallar flera</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2960,37 +2960,43 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126856452</v>
+        <v>126856543</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2998,10 +3004,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443002</v>
+        <v>443237</v>
       </c>
       <c r="R23" t="n">
-        <v>6764790</v>
+        <v>6765007</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3061,43 +3067,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126856543</v>
+        <v>126856452</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443237</v>
+        <v>443002</v>
       </c>
       <c r="R24" t="n">
-        <v>6765007</v>
+        <v>6764790</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -3269,37 +3269,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126856468</v>
+        <v>126856650</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3307,10 +3312,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443011</v>
+        <v>443118</v>
       </c>
       <c r="R26" t="n">
-        <v>6764818</v>
+        <v>6764972</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3351,7 +3356,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3370,42 +3374,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126856650</v>
+        <v>126856468</v>
       </c>
       <c r="B27" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3413,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443118</v>
+        <v>443011</v>
       </c>
       <c r="R27" t="n">
-        <v>6764972</v>
+        <v>6764818</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3457,6 +3456,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126807124</v>
       </c>
       <c r="B4" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>126806915</v>
       </c>
       <c r="B10" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2310,45 +2310,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126806993</v>
+        <v>126807104</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443056</v>
+        <v>443143</v>
       </c>
       <c r="R17" t="n">
-        <v>6764863</v>
+        <v>6764853</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Tjäderbetat tallar flera</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126808925</v>
+        <v>126806993</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,39 +2433,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443278</v>
+        <v>443056</v>
       </c>
       <c r="R18" t="n">
-        <v>6764930</v>
+        <v>6764863</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2497,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2502,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tallar flera</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,45 +2534,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126807104</v>
+        <v>126808925</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443143</v>
+        <v>443278</v>
       </c>
       <c r="R19" t="n">
-        <v>6764853</v>
+        <v>6764930</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2604,7 +2609,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,12 +2619,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2960,43 +2960,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126856543</v>
+        <v>126856452</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3004,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443237</v>
+        <v>443002</v>
       </c>
       <c r="R23" t="n">
-        <v>6765007</v>
+        <v>6764790</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3067,37 +3061,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126856452</v>
+        <v>126856543</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443002</v>
+        <v>443237</v>
       </c>
       <c r="R24" t="n">
-        <v>6764790</v>
+        <v>6765007</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3269,42 +3269,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126856650</v>
+        <v>126856468</v>
       </c>
       <c r="B26" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3312,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443118</v>
+        <v>443011</v>
       </c>
       <c r="R26" t="n">
-        <v>6764972</v>
+        <v>6764818</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3356,6 +3351,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3374,37 +3370,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126856468</v>
+        <v>126856650</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3412,10 +3413,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443011</v>
+        <v>443118</v>
       </c>
       <c r="R27" t="n">
-        <v>6764818</v>
+        <v>6764972</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3456,7 +3457,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3576,37 +3576,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126856520</v>
+        <v>126856594</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3614,10 +3620,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443109</v>
+        <v>443105</v>
       </c>
       <c r="R29" t="n">
-        <v>6764976</v>
+        <v>6764965</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3677,43 +3683,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126856594</v>
+        <v>126856520</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443105</v>
+        <v>443109</v>
       </c>
       <c r="R30" t="n">
-        <v>6764965</v>
+        <v>6764976</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126807174</v>
+        <v>126807124</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443147</v>
+        <v>443128</v>
       </c>
       <c r="R3" t="n">
-        <v>6764845</v>
+        <v>6764859</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126807124</v>
+        <v>126807174</v>
       </c>
       <c r="B4" t="n">
-        <v>91346</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443128</v>
+        <v>443147</v>
       </c>
       <c r="R4" t="n">
-        <v>6764859</v>
+        <v>6764845</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126807192</v>
+        <v>126806915</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>91346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443147</v>
+        <v>443009</v>
       </c>
       <c r="R9" t="n">
-        <v>6764845</v>
+        <v>6764878</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126806915</v>
+        <v>126806622</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>56849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443009</v>
+        <v>442916</v>
       </c>
       <c r="R10" t="n">
-        <v>6764878</v>
+        <v>6764851</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,45 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126806622</v>
+        <v>126807192</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442916</v>
+        <v>443147</v>
       </c>
       <c r="R11" t="n">
-        <v>6764851</v>
+        <v>6764845</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,12 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126807124</v>
+        <v>126807174</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>78772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443128</v>
+        <v>443147</v>
       </c>
       <c r="R3" t="n">
-        <v>6764859</v>
+        <v>6764845</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126807174</v>
+        <v>126807124</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>91346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443147</v>
+        <v>443128</v>
       </c>
       <c r="R4" t="n">
-        <v>6764845</v>
+        <v>6764859</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126806915</v>
+        <v>126806622</v>
       </c>
       <c r="B9" t="n">
-        <v>91346</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443009</v>
+        <v>442916</v>
       </c>
       <c r="R9" t="n">
-        <v>6764878</v>
+        <v>6764851</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,45 +1551,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126806622</v>
+        <v>126807192</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442916</v>
+        <v>443147</v>
       </c>
       <c r="R10" t="n">
-        <v>6764851</v>
+        <v>6764845</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,12 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126807192</v>
+        <v>126806915</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>91346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443147</v>
+        <v>443009</v>
       </c>
       <c r="R11" t="n">
-        <v>6764845</v>
+        <v>6764878</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3576,43 +3576,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126856594</v>
+        <v>126856520</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3620,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443105</v>
+        <v>443109</v>
       </c>
       <c r="R29" t="n">
-        <v>6764965</v>
+        <v>6764976</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3683,37 +3677,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126856520</v>
+        <v>126856594</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443109</v>
+        <v>443105</v>
       </c>
       <c r="R30" t="n">
-        <v>6764976</v>
+        <v>6764965</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -2091,50 +2091,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126806928</v>
+        <v>126809036</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>78773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443009</v>
+        <v>443235</v>
       </c>
       <c r="R15" t="n">
-        <v>6764877</v>
+        <v>6764959</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2166,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2171,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2198,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126809036</v>
+        <v>126806928</v>
       </c>
       <c r="B16" t="n">
-        <v>78773</v>
+        <v>8447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443235</v>
+        <v>443009</v>
       </c>
       <c r="R16" t="n">
-        <v>6764959</v>
+        <v>6764877</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126807174</v>
+        <v>126807124</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443147</v>
+        <v>443128</v>
       </c>
       <c r="R3" t="n">
-        <v>6764845</v>
+        <v>6764859</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126807124</v>
+        <v>126807174</v>
       </c>
       <c r="B4" t="n">
-        <v>91346</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443128</v>
+        <v>443147</v>
       </c>
       <c r="R4" t="n">
-        <v>6764859</v>
+        <v>6764845</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126807488</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126807124</v>
+        <v>126807174</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443128</v>
+        <v>443147</v>
       </c>
       <c r="R3" t="n">
-        <v>6764859</v>
+        <v>6764845</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126807174</v>
+        <v>126807124</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443147</v>
+        <v>443128</v>
       </c>
       <c r="R4" t="n">
-        <v>6764845</v>
+        <v>6764859</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>126806596</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126807138</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126809153</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>126809061</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,45 +1439,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126806622</v>
+        <v>126807192</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>78777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442916</v>
+        <v>443147</v>
       </c>
       <c r="R9" t="n">
-        <v>6764851</v>
+        <v>6764845</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,12 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,45 +1546,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126807192</v>
+        <v>126806622</v>
       </c>
       <c r="B10" t="n">
-        <v>78773</v>
+        <v>56853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443147</v>
+        <v>442916</v>
       </c>
       <c r="R10" t="n">
-        <v>6764845</v>
+        <v>6764851</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1626,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,7 +1661,7 @@
         <v>126806915</v>
       </c>
       <c r="B11" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>126807424</v>
       </c>
       <c r="B12" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126807279</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126807368</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,45 +2091,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126809036</v>
+        <v>126806928</v>
       </c>
       <c r="B15" t="n">
-        <v>78773</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443235</v>
+        <v>443009</v>
       </c>
       <c r="R15" t="n">
-        <v>6764959</v>
+        <v>6764877</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2161,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2171,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,50 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126806928</v>
+        <v>126809036</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>78777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443009</v>
+        <v>443235</v>
       </c>
       <c r="R16" t="n">
-        <v>6764877</v>
+        <v>6764959</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,7 +2313,7 @@
         <v>126807104</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126806993</v>
+        <v>126808925</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,34 +2433,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443056</v>
+        <v>443278</v>
       </c>
       <c r="R18" t="n">
-        <v>6764863</v>
+        <v>6764930</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2492,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,12 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tallar flera</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126808925</v>
+        <v>126806993</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>56853</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,39 +2545,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443278</v>
+        <v>443056</v>
       </c>
       <c r="R19" t="n">
-        <v>6764930</v>
+        <v>6764863</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2609,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2619,7 +2614,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tallar flera</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2649,7 @@
         <v>126809217</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>126856440</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>126856462</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>126856452</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>126856543</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>126856401</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>126856468</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>126856650</v>
       </c>
       <c r="B27" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126856408</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>126856520</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>126856594</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>126856433</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>126856512</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -1439,45 +1439,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126807192</v>
+        <v>126806622</v>
       </c>
       <c r="B9" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443147</v>
+        <v>442916</v>
       </c>
       <c r="R9" t="n">
-        <v>6764845</v>
+        <v>6764851</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1551,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126806622</v>
+        <v>126806915</v>
       </c>
       <c r="B10" t="n">
-        <v>56853</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442916</v>
+        <v>443009</v>
       </c>
       <c r="R10" t="n">
-        <v>6764851</v>
+        <v>6764878</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,12 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126806915</v>
+        <v>126807192</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443009</v>
+        <v>443147</v>
       </c>
       <c r="R11" t="n">
-        <v>6764878</v>
+        <v>6764845</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126808925</v>
+        <v>126806993</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>56853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,39 +2433,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443278</v>
+        <v>443056</v>
       </c>
       <c r="R18" t="n">
-        <v>6764930</v>
+        <v>6764863</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2497,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2502,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tallar flera</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126806993</v>
+        <v>126808925</v>
       </c>
       <c r="B19" t="n">
-        <v>56853</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,34 +2545,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443056</v>
+        <v>443278</v>
       </c>
       <c r="R19" t="n">
-        <v>6764863</v>
+        <v>6764930</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2604,7 +2609,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,12 +2619,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tallar flera</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126807174</v>
+        <v>126807124</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443147</v>
+        <v>443128</v>
       </c>
       <c r="R3" t="n">
-        <v>6764845</v>
+        <v>6764859</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126807124</v>
+        <v>126807174</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>78776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443128</v>
+        <v>443147</v>
       </c>
       <c r="R4" t="n">
-        <v>6764859</v>
+        <v>6764845</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126806622</v>
+        <v>126806915</v>
       </c>
       <c r="B9" t="n">
-        <v>56853</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442916</v>
+        <v>443009</v>
       </c>
       <c r="R9" t="n">
-        <v>6764851</v>
+        <v>6764878</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,12 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126806915</v>
+        <v>126807192</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>78777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443009</v>
+        <v>443147</v>
       </c>
       <c r="R10" t="n">
-        <v>6764878</v>
+        <v>6764845</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,45 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126807192</v>
+        <v>126806622</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443147</v>
+        <v>442916</v>
       </c>
       <c r="R11" t="n">
-        <v>6764845</v>
+        <v>6764851</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1728,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1733,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -3576,37 +3576,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126856520</v>
+        <v>126856594</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3614,10 +3620,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443109</v>
+        <v>443105</v>
       </c>
       <c r="R29" t="n">
-        <v>6764976</v>
+        <v>6764965</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3677,43 +3683,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126856594</v>
+        <v>126856520</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443105</v>
+        <v>443109</v>
       </c>
       <c r="R30" t="n">
-        <v>6764965</v>
+        <v>6764976</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -3576,43 +3576,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126856594</v>
+        <v>126856520</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3620,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443105</v>
+        <v>443109</v>
       </c>
       <c r="R29" t="n">
-        <v>6764965</v>
+        <v>6764976</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3683,37 +3677,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126856520</v>
+        <v>126856594</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443109</v>
+        <v>443105</v>
       </c>
       <c r="R30" t="n">
-        <v>6764976</v>
+        <v>6764965</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -2758,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126856440</v>
+        <v>126856462</v>
       </c>
       <c r="B21" t="n">
         <v>79018</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442971</v>
+        <v>442988</v>
       </c>
       <c r="R21" t="n">
-        <v>6764763</v>
+        <v>6764821</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126856462</v>
+        <v>126856440</v>
       </c>
       <c r="B22" t="n">
         <v>79018</v>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442988</v>
+        <v>442971</v>
       </c>
       <c r="R22" t="n">
-        <v>6764821</v>
+        <v>6764763</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126807488</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126807124</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126807174</v>
       </c>
       <c r="B4" t="n">
-        <v>78776</v>
+        <v>78769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126806596</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126807138</v>
       </c>
       <c r="B6" t="n">
-        <v>78776</v>
+        <v>78769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126809153</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>126809061</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126806915</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>126807192</v>
       </c>
       <c r="B10" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>126806622</v>
       </c>
       <c r="B11" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>126807424</v>
       </c>
       <c r="B12" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126807279</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126807368</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>78769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>126806928</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>126809036</v>
       </c>
       <c r="B16" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,45 +2310,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126807104</v>
+        <v>126806993</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443143</v>
+        <v>443056</v>
       </c>
       <c r="R17" t="n">
-        <v>6764853</v>
+        <v>6764863</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tallstammen</t>
+          <t>Tjäderbetat tallar flera</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126806993</v>
+        <v>126808925</v>
       </c>
       <c r="B18" t="n">
-        <v>56853</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,34 +2433,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443056</v>
+        <v>443278</v>
       </c>
       <c r="R18" t="n">
-        <v>6764863</v>
+        <v>6764930</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2492,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,12 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tjäderbetat tallar flera</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,50 +2534,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126808925</v>
+        <v>126807104</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443278</v>
+        <v>443143</v>
       </c>
       <c r="R19" t="n">
-        <v>6764930</v>
+        <v>6764853</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2609,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2619,7 +2614,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2649,7 @@
         <v>126809217</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126856462</v>
+        <v>126856440</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442988</v>
+        <v>442971</v>
       </c>
       <c r="R21" t="n">
-        <v>6764821</v>
+        <v>6764763</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126856440</v>
+        <v>126856462</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442971</v>
+        <v>442988</v>
       </c>
       <c r="R22" t="n">
-        <v>6764763</v>
+        <v>6764821</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2963,7 +2963,7 @@
         <v>126856452</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>126856543</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>126856401</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>126856468</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>126856650</v>
       </c>
       <c r="B27" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126856408</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>126856520</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>126856594</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>126856433</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>126856512</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 29380-2025 artfynd.xlsx
+++ b/artfynd/A 29380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126807488</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126807124</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126807174</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126806596</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126807138</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126809153</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>126809061</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126806915</v>
       </c>
       <c r="B9" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>126807192</v>
       </c>
       <c r="B10" t="n">
-        <v>78770</v>
+        <v>78777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>126806622</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>126807424</v>
       </c>
       <c r="B12" t="n">
-        <v>78770</v>
+        <v>78777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>126807279</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126807368</v>
       </c>
       <c r="B14" t="n">
-        <v>78769</v>
+        <v>78776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>126806928</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>126809036</v>
       </c>
       <c r="B16" t="n">
-        <v>78770</v>
+        <v>78777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,45 +2310,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126806993</v>
+        <v>126807104</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
+          <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443056</v>
+        <v>443143</v>
       </c>
       <c r="R17" t="n">
-        <v>6764863</v>
+        <v>6764853</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Tjäderbetat tallar flera</t>
+          <t>På tallstammen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126808925</v>
+        <v>126806993</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>56853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,39 +2433,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Österklikten, Österklikten, Dlr</t>
+          <t>Klikttjärnen, Klikttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443278</v>
+        <v>443056</v>
       </c>
       <c r="R18" t="n">
-        <v>6764930</v>
+        <v>6764863</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2497,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2502,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tjäderbetat tallar flera</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,45 +2534,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126807104</v>
+        <v>126808925</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Österklikten, Österklikten, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443143</v>
+        <v>443278</v>
       </c>
       <c r="R19" t="n">
-        <v>6764853</v>
+        <v>6764930</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2604,7 +2609,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,12 +2619,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallstammen</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2649,7 @@
         <v>126809217</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126856440</v>
+        <v>126856462</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442971</v>
+        <v>442988</v>
       </c>
       <c r="R21" t="n">
-        <v>6764763</v>
+        <v>6764821</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126856462</v>
+        <v>126856440</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442988</v>
+        <v>442971</v>
       </c>
       <c r="R22" t="n">
-        <v>6764821</v>
+        <v>6764763</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2963,7 +2963,7 @@
         <v>126856452</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>126856543</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>126856401</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>126856468</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>126856650</v>
       </c>
       <c r="B27" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126856408</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>126856520</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>126856594</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>126856433</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>126856512</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
